--- a/DATA/MASTER/C11_MASTER/Preparacion_Machine_Learning/ipm/clasificacion_ipml.xlsx
+++ b/DATA/MASTER/C11_MASTER/Preparacion_Machine_Learning/ipm/clasificacion_ipml.xlsx
@@ -486,42 +486,42 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Puntaje_Redundancia</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Puntaje_Multicolinealidad</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Importancia</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Puntaje_Conocimiento_Dominio</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>% Cobertura</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Puntaje_Calidad</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Puntaje_Redundancia</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Puntaje_Multicolinealidad</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Precipitacion_mm</t>
+          <t>ONI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -572,11 +572,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.898</v>
+        <v>2.084</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -585,38 +585,38 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Climática</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Variabilidad Climática</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
         <v>100</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -646,7 +646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ONI</t>
+          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -667,11 +667,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.265</v>
+        <v>3.619</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -680,38 +680,38 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Variabilidad Climática</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
         <v>3</v>
       </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
         <v>100</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,7 +741,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Radiacion_Solar</t>
+          <t>Precipitacion_mm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -762,11 +762,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.704</v>
+        <v>1.99</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -775,38 +775,38 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
         <v>3</v>
       </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
         <v>100</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -836,7 +836,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Humedad_Relativa</t>
+          <t>Radiacion_Solar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -857,57 +857,57 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7.128</v>
+        <v>2.449</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Existe una dependencia moderada aceptable para modelado.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Sin restricciones importantes.</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
         <v>100</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
       <c r="S5" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nivel_Minimo</t>
+          <t>irca</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -952,11 +952,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.027</v>
+        <v>2.144</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -965,44 +965,44 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Hidrológica</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
         <v>3</v>
       </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>16.48</v>
-      </c>
       <c r="Q6" t="n">
-        <v>0.165</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9165</v>
+        <v>1</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Pendiente por Cobertura</t>
+          <t>Seleccionada</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Cobertura inferior al umbral mínimo establecido.</t>
+          <t>Cumple todos los criterios del Framework.</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1047,11 +1047,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.815</v>
+        <v>2.114</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1060,44 +1060,44 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Hidrológica</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
         <v>3</v>
       </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>9.470000000000001</v>
-      </c>
       <c r="Q7" t="n">
-        <v>0.095</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>63.64</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0.636</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9095</v>
+        <v>0.9636</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Pendiente por Cobertura</t>
+          <t>Seleccionada</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Cobertura inferior al umbral mínimo establecido.</t>
+          <t>Cumple todos los criterios del Framework.</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+          <t>Humedad_Relativa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1142,57 +1142,57 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.97</v>
+        <v>9.391</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
         <v>3</v>
       </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>9.279999999999999</v>
-      </c>
       <c r="Q8" t="n">
-        <v>0.093</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9093</v>
+        <v>0.95</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Pendiente por Cobertura</t>
+          <t>Seleccionada</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Cobertura inferior al umbral mínimo establecido.</t>
+          <t>Cumple todos los criterios del Framework.</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Temp_Min_C</t>
+          <t>Nivel_Minimo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1237,57 +1237,57 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>10.573</v>
+        <v>1.028</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Climática</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Hidrológica</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
         <v>3</v>
       </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>100</v>
-      </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>16.48</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5</v>
+        <v>0.165</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9</v>
+        <v>0.9165</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Seleccionada</t>
+          <t>Pendiente por Cobertura</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Cumple todos los criterios del Framework.</t>
+          <t>Cobertura inferior al umbral mínimo establecido.</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AGUAS RESIDUALES TRATADAS</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1332,11 +1332,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.63</v>
+        <v>2.878</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1345,48 +1345,48 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
         <v>3</v>
       </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>18.18</v>
-      </c>
       <c r="Q10" t="n">
-        <v>0.182</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.833</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0.095</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8681</v>
+        <v>0.9095</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mes</t>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1427,11 +1427,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.152</v>
+        <v>2.999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1440,58 +1440,58 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Temporal</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.667</v>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
       </c>
       <c r="P11" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0.093</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8668</v>
+        <v>0.9093</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Seleccionada</t>
+          <t>Pendiente por Cobertura</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Cumple todos los criterios del Framework.</t>
+          <t>Cobertura inferior al umbral mínimo establecido.</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Velocidad_Viento</t>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1522,11 +1522,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.477</v>
+        <v>1.965</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1535,58 +1535,58 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Climática</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.667</v>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
       </c>
       <c r="P12" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>4.92</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0.049</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8668</v>
+        <v>0.9049</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Seleccionada</t>
+          <t>Pendiente por Cobertura</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Cumple todos los criterios del Framework.</t>
+          <t>Cobertura inferior al umbral mínimo establecido.</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>irca</t>
+          <t>Temp_Min_C</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1605,10 +1605,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1617,11 +1617,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>13.982</v>
+        <v>13.221</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1630,48 +1630,48 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta multicolinealidad alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
+          <t>Considerar la dependencia lineal en la evaluación posterior.</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
         <v>3</v>
       </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
         <v>100</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.833</v>
-      </c>
       <c r="S13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8499</v>
+        <v>0.9</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VolumenUtilDiarioMasa</t>
+          <t>Mes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1712,57 +1712,57 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>11.557</v>
+        <v>1.25</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Analizar conjuntamente con otras variables.</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Hidrológica</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
       <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R14" t="n">
         <v>100</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.833</v>
-      </c>
       <c r="S14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8499</v>
+        <v>0.8668</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CALIDAD DEL AGUA</t>
+          <t>Velocidad_Viento</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1795,69 +1795,69 @@
         </is>
       </c>
       <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Muy Baja</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>2.574</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Baja redundancia estructural.</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>4.372</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Variable con baja dependencia estructural.</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>3</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>18.18</v>
-      </c>
       <c r="Q15" t="n">
-        <v>0.182</v>
+        <v>0.667</v>
       </c>
       <c r="R15" t="n">
-        <v>0.667</v>
+        <v>100</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8183</v>
+        <v>0.8668</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Pendiente por Cobertura</t>
+          <t>Seleccionada</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Cobertura inferior al umbral mínimo establecido.</t>
+          <t>Cumple todos los criterios del Framework.</t>
         </is>
       </c>
     </row>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1902,11 +1902,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>7.427</v>
+        <v>7.54</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1915,44 +1915,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Existe una dependencia moderada aceptable para modelado.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Sin restricciones importantes.</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Calidad del Agua</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
         <v>3</v>
       </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
         <v>9.470000000000001</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.095</v>
       </c>
-      <c r="R16" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.75</v>
-      </c>
       <c r="T16" t="n">
-        <v>0.8094</v>
+        <v>0.8595</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+          <t>SOLIDOS SUSPENDIDOS TOTALES</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1985,83 +1985,83 @@
         </is>
       </c>
       <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Muy Baja</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Baja redundancia estructural.</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>1.934</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Variable con baja dependencia estructural.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>4.92</v>
-      </c>
       <c r="Q17" t="n">
-        <v>0.049</v>
+        <v>0.667</v>
       </c>
       <c r="R17" t="n">
-        <v>0.667</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0.095</v>
       </c>
       <c r="T17" t="n">
-        <v>0.805</v>
+        <v>0.7763</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Pendiente por Cobertura</t>
+          <t>No Prioritaria</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Cobertura inferior al umbral mínimo establecido.</t>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Temp_Max_C</t>
+          <t>TEMPERATURA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2092,57 +2092,57 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>31.915</v>
+        <v>2.965</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Climática</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
       </c>
       <c r="P18" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="R18" t="n">
-        <v>0.833</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>0.25</v>
+        <v>0.095</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.7763</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Temp_Media_C</t>
+          <t>TURBIDEZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2187,57 +2187,57 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>36.048</v>
+        <v>1.645</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Climática</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>3</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
       </c>
       <c r="P19" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="R19" t="n">
-        <v>0.833</v>
+        <v>6.44</v>
       </c>
       <c r="S19" t="n">
-        <v>0.25</v>
+        <v>0.064</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.7732</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TEMPERATURA</t>
+          <t>Anio</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2282,11 +2282,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.883</v>
+        <v>4.188</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2295,44 +2295,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.667</v>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
       </c>
       <c r="P20" t="n">
-        <v>9.470000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.095</v>
+        <v>0.333</v>
       </c>
       <c r="R20" t="n">
-        <v>0.833</v>
+        <v>100</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7262</v>
+        <v>0.7332</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SOLIDOS SUSPENDIDOS TOTALES</t>
+          <t>CALIDAD DEL AGUA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2368,66 +2368,66 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2.705</v>
+        <v>6.742</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>Calidad del Agua</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N21" t="n">
-        <v>2</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.667</v>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
       </c>
       <c r="P21" t="n">
-        <v>9.470000000000001</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.095</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0.833</v>
+        <v>18.18</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0.182</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7262</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TURBIDEZ</t>
+          <t>COBERTURA DE ALCANTARILLADO URBANO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2463,20 +2463,20 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.619</v>
+        <v>3.032</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2485,44 +2485,44 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>2</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>0.667</v>
       </c>
-      <c r="P22" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.064</v>
-      </c>
       <c r="R22" t="n">
-        <v>0.833</v>
+        <v>100</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7231</v>
+        <v>0.7168</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Anio</t>
+          <t>ACCESO A AGUA POTABLE ADECUADO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2555,73 +2555,73 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.779</v>
+        <v>37.091</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Existe una dependencia moderada aceptable para modelado.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Sin restricciones importantes.</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Temporal</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>100</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U23" t="inlineStr">
         <is>
           <t>Media</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.6832</v>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Baja</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CONTINUIDAD DE ACUEDUCTO URBANO</t>
+          <t>Temp_Max_C</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2650,23 +2650,23 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2354914.55</v>
+        <v>36.388</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2675,48 +2675,48 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.667</v>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
       </c>
       <c r="P24" t="n">
-        <v>18.18</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.182</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="S24" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>0.635</v>
+        <v>0.7</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FOSFORO TOTAL</t>
+          <t>Temp_Media_C</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2748,70 +2748,70 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>14.153</v>
+        <v>82.34</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.667</v>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
       </c>
       <c r="P25" t="n">
-        <v>9.279999999999999</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.093</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.833</v>
+        <v>100</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0.626</v>
+        <v>0.7</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NITROGENO TOTAL</t>
+          <t>CONTINUIDAD DE ACUEDUCTO URBANO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2852,57 +2852,55 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>10.296</v>
-      </c>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
+          <t>No Calculado</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>VIF no calculable por varianza nula de la variable.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Evaluar por separado debido a varianza nula; el VIF no es calculable.</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Analizar conjuntamente con otras variables.</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>2</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.667</v>
       </c>
-      <c r="P26" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.055</v>
-      </c>
       <c r="R26" t="n">
-        <v>0.833</v>
+        <v>18.18</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5</v>
+        <v>0.182</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6222</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -2926,7 +2924,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CONDUCTIVIDAD ELECTRICA</t>
+          <t>NITROGENO TOTAL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2935,69 +2933,69 @@
         </is>
       </c>
       <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Muy Baja</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>10.278</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Se detecta multicolinealidad alta respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Considerar la dependencia lineal en la evaluación posterior.</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
         <v>2</v>
       </c>
-      <c r="E27" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Baja redundancia estructural.</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>22.078</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N27" t="n">
-        <v>2</v>
-      </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.667</v>
       </c>
-      <c r="P27" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0.095</v>
-      </c>
       <c r="R27" t="n">
-        <v>0.667</v>
+        <v>5.49</v>
       </c>
       <c r="S27" t="n">
-        <v>0.25</v>
+        <v>0.055</v>
       </c>
       <c r="T27" t="n">
-        <v>0.5264</v>
+        <v>0.6723</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -3021,7 +3019,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>INDICE DE DESEMPENO INSTITUCIONAL</t>
+          <t>COBERTURA DE ALCANTARILLADO RURAL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3030,69 +3028,69 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.833</v>
+        <v>0.5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4.434</v>
+        <v>7.181</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Institucional</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.667</v>
       </c>
-      <c r="P28" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0.091</v>
-      </c>
       <c r="R28" t="n">
-        <v>0.167</v>
+        <v>100</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.526</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -3116,7 +3114,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ACCESO A AGUA POTABLE ADECUADO</t>
+          <t>AGUAS RESIDUALES TRATADAS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3125,7 +3123,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -3137,59 +3135,57 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en el máximo relativo de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>5.555</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
         <v>3</v>
       </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>100</v>
-      </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>18.18</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="T29" t="n">
-        <v>0.5</v>
+        <v>0.5682</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -3213,7 +3209,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
+          <t>COBERTURA DE ACUEDUCTO RURAL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3222,71 +3218,69 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>32.439</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N30" t="n">
-        <v>3</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1</v>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
       </c>
       <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R30" t="n">
         <v>100</v>
       </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.5</v>
+        <v>0.5668</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -3310,7 +3304,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DENSIDAD POBLACIONAL</t>
+          <t>COBERTURA DE ACUEDUCTO URBANO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3319,71 +3313,69 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>42.952</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Demográfica</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>2</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>0.667</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>100</v>
       </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.3668</v>
+        <v>0.5668</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -3407,7 +3399,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>COBERTURA DE ACUEDUCTO RURAL</t>
+          <t>DENSIDAD POBLACIONAL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3416,71 +3408,69 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1329.161</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Demográfica</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>2</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>0.667</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>100</v>
       </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0.3668</v>
+        <v>0.5668</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -3504,7 +3494,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>COBERTURA DE ACUEDUCTO URBANO</t>
+          <t>POBLACION TOTAL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3513,71 +3503,69 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1182.398</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Demográfica</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>2</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.667</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>100</v>
       </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0.3668</v>
+        <v>0.5668</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -3601,7 +3589,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>COBERTURA DE ALCANTARILLADO RURAL</t>
+          <t>FOSFORO TOTAL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3610,71 +3598,69 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>14.559</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
+          <t>Considerar la dependencia lineal en la evaluación posterior.</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>2</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>0.667</v>
       </c>
-      <c r="P34" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="T34" t="n">
-        <v>0.3668</v>
+        <v>0.5261</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -3698,7 +3684,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>COBERTURA DE ALCANTARILLADO URBANO</t>
+          <t>CONDUCTIVIDAD ELECTRICA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3707,71 +3693,69 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>22.148</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>2</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.667</v>
       </c>
-      <c r="P35" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="T35" t="n">
-        <v>0.3668</v>
+        <v>0.4763</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -3795,7 +3779,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>POBLACION TOTAL</t>
+          <t>INDICE DE DESEMPENO INSTITUCIONAL</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3804,52 +3788,70 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Demográfica</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
+          <t>Participa en el máximo relativo de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>8.381</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Institucional</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>2</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>0.667</v>
       </c>
-      <c r="P36" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
       <c r="R36" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+        <v>9.09</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.4259</v>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>Baja</t>
@@ -3857,10 +3859,14 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>No Evaluada</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr"/>
+          <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
